--- a/astro-site/public/dl/pack-appcc/05-checklist-recepcion-mercancias.xlsx
+++ b/astro-site/public/dl/pack-appcc/05-checklist-recepcion-mercancias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Recepción Mercancías" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recepción Mercancías" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -115,27 +115,27 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -495,15 +495,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -511,6 +512,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -518,9 +520,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -549,9 +549,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -559,9 +557,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr"/>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -597,13 +593,19 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" t="inlineStr"/>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -611,7 +613,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -620,22 +631,22 @@
   <sheetPr>
     <tabColor rgb="00FF9800"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="14"/>
-    <col customWidth="1" max="2" min="2" width="22"/>
-    <col customWidth="1" max="3" min="3" width="20"/>
-    <col customWidth="1" max="4" min="4" width="12"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
-    <col customWidth="1" max="8" min="8" width="12"/>
-    <col customWidth="1" max="9" min="9" width="12"/>
-    <col customWidth="1" max="10" min="10" width="12"/>
-    <col customWidth="1" max="11" min="11" width="20"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -652,6 +663,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1034,6 +1046,7 @@
       <c r="J29" s="7" t="n"/>
       <c r="K29" s="7" t="n"/>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
@@ -1053,14 +1066,22 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29" type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,✗"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29" type="list">
+    <dataValidation sqref="J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SÍ,NO"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/pack-appcc/05-checklist-recepcion-mercancias.xlsx
+++ b/astro-site/public/dl/pack-appcc/05-checklist-recepcion-mercancias.xlsx
@@ -10,15 +10,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recepción Mercancías" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$30</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Recepción Mercancías'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Recepción Mercancías'!$A$1:$N$48</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="9">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,8 +76,31 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -90,8 +119,18 @@
         <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -113,11 +152,25 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,10 +184,74 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -497,16 +614,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Checklist de Recepción de Mercancías</t>
         </is>
@@ -514,7 +631,7 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla</t>
         </is>
@@ -522,98 +639,134 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>▸ Verifica CADA entrega de mercancía con este checklist</t>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>▸ Verifica CADA entrega con este checklist y fírmalo: la columna «Firma receptor» es la que acredita quién hizo la comprobación.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>▸ Controla: temperatura, caducidad, etiquetado, estado envase, cantidad</t>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>▸ Anota el «Nº albarán» y el «Nº lote». Son las dos claves que enganchan esta hoja con el registro 06 de trazabilidad; sin ellas, una retirada de lote no se puede reconstruir.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ Si algo no cumple: RECHAZAR y registrar incidencia</t>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>▸ Las cuatro columnas de verificación admiten ✓, ✗ o N/A y se pintan solas (verde / rojo). Si escribes otra cosa, el desplegable la rechaza.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>▸ Conserva los albaranes junto con este registro</t>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>▸ Si algo no cumple: RECHAZAR la entrega y abrir la incidencia en el registro 11 (Acciones Correctivas).</t>
         </is>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Puntos críticos de recepción</t>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Qué se comprueba en cada entrega</t>
         </is>
       </c>
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>▸ Temperatura: medir con termómetro de sonda (calibrado)</t>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>▸ Temperatura: con termómetro de sonda verificado (registro 19). El veredicto por familia está en el registro 02.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>▸ Caducidad: mínimo 2/3 de vida útil restante</t>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>▸ Caducidad: al menos 2/3 de vida útil restante.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>▸ Etiquetado: lote, origen, ingredientes, alérgenos</t>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>▸ Etiquetado: lote, origen, ingredientes y alérgenos.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>▸ Envase: sin golpes, roturas ni hinchazón</t>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>▸ Envase: sin golpes, roturas ni hinchazón.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>▸ Olor/aspecto: sin signos de deterioro</t>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>▸ Aspecto y olor: sin signos de deterioro.</t>
         </is>
       </c>
     </row>
     <row r="18"/>
     <row r="19">
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Relación con el registro 02</t>
         </is>
       </c>
     </row>
     <row r="20"/>
     <row r="21">
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>El 02 es el punto de control crítico de TEMPERATURA en recepción y el 05 es la verificación DOCUMENTAL de la misma entrega. No se fusionan: son dos registros distintos, con dos tarjetas distintas en tu panel, y una inspección puede pedir cualquiera de los dos por separado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Frecuencia y archivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>▸ Frecuencia: una fila por entrega. La hoja trae 40 filas (aprox. un mes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>▸ Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2"/>
-  </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
@@ -633,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,11 +799,14 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Checklist de Recepción de Mercancías</t>
         </is>
@@ -664,416 +820,943 @@
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Temp. (°C)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Caducidad</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>Etiquetado OK</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>Envase OK</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>Aspecto OK</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>Cantidad OK</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>Aceptado</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>Nº albarán</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Nº lote</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Firma receptor</t>
+        </is>
+      </c>
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="7" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="7" t="n"/>
-      <c r="J24" s="7" t="n"/>
-      <c r="K24" s="7" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="7" t="n"/>
-      <c r="J25" s="7" t="n"/>
-      <c r="K25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="7" t="n"/>
-      <c r="J26" s="7" t="n"/>
-      <c r="K26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n"/>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="7" t="n"/>
-      <c r="J29" s="7" t="n"/>
-      <c r="K29" s="7" t="n"/>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Conservar junto con albaranes de entrega. Archivo mínimo: 2 años.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Merluza fresca</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Pescados de la Ría S.L.</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>ALB-2026-4471</t>
+        </is>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>L-2026-0912</t>
+        </is>
+      </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>A.R.</t>
+        </is>
+      </c>
+      <c r="N5" s="15" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Canal de ternera</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Cárnicas del Norte</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>ALB-2026-4472</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>L-2026-0913</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
+        <is>
+          <t>A.R.</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Guisantes congelados</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Congelados del Sur</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>03/2028</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>ALB-2026-4473</t>
+        </is>
+      </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>L-2026-0914</t>
+        </is>
+      </c>
+      <c r="M7" s="14" t="inlineStr">
+        <is>
+          <t>A.R.</t>
+        </is>
+      </c>
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t>Envase roto y cadena de frío rota · incidencia INC-002 (ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="14" t="n"/>
+      <c r="J8" s="14" t="n"/>
+      <c r="K8" s="14" t="n"/>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="14" t="n"/>
+      <c r="N8" s="15" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="14" t="n"/>
+      <c r="H9" s="14" t="n"/>
+      <c r="I9" s="14" t="n"/>
+      <c r="J9" s="14" t="n"/>
+      <c r="K9" s="14" t="n"/>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="14" t="n"/>
+      <c r="N9" s="15" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="14" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="14" t="n"/>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="14" t="n"/>
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="14" t="n"/>
+      <c r="N10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="14" t="n"/>
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
+      <c r="N11" s="15" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="14" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="14" t="n"/>
+      <c r="J12" s="14" t="n"/>
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="14" t="n"/>
+      <c r="N12" s="15" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="14" t="n"/>
+      <c r="J13" s="14" t="n"/>
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="14" t="n"/>
+      <c r="M13" s="14" t="n"/>
+      <c r="N13" s="15" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="14" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="14" t="n"/>
+      <c r="J14" s="14" t="n"/>
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="14" t="n"/>
+      <c r="M14" s="14" t="n"/>
+      <c r="N14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="14" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="n"/>
+      <c r="J15" s="14" t="n"/>
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="14" t="n"/>
+      <c r="M15" s="14" t="n"/>
+      <c r="N15" s="15" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
+      <c r="J16" s="14" t="n"/>
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="15" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="14" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="15" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="14" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="14" t="n"/>
+      <c r="N19" s="15" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="14" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
+      <c r="N21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="14" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
+      <c r="N22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="14" t="n"/>
+      <c r="L23" s="14" t="n"/>
+      <c r="M23" s="14" t="n"/>
+      <c r="N23" s="15" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="14" t="n"/>
+      <c r="M24" s="14" t="n"/>
+      <c r="N24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="14" t="n"/>
+      <c r="J25" s="14" t="n"/>
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="14" t="n"/>
+      <c r="M25" s="14" t="n"/>
+      <c r="N25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="14" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="14" t="n"/>
+      <c r="I26" s="14" t="n"/>
+      <c r="J26" s="14" t="n"/>
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="14" t="n"/>
+      <c r="M26" s="14" t="n"/>
+      <c r="N26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="14" t="n"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="14" t="n"/>
+      <c r="H27" s="14" t="n"/>
+      <c r="I27" s="14" t="n"/>
+      <c r="J27" s="14" t="n"/>
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="14" t="n"/>
+      <c r="M27" s="14" t="n"/>
+      <c r="N27" s="15" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="14" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="14" t="n"/>
+      <c r="M28" s="14" t="n"/>
+      <c r="N28" s="15" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="14" t="n"/>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
+      <c r="L29" s="14" t="n"/>
+      <c r="M29" s="14" t="n"/>
+      <c r="N29" s="15" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="14" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
+      <c r="L30" s="14" t="n"/>
+      <c r="M30" s="14" t="n"/>
+      <c r="N30" s="15" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
+      <c r="L31" s="14" t="n"/>
+      <c r="M31" s="14" t="n"/>
+      <c r="N31" s="15" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="14" t="n"/>
+      <c r="L32" s="14" t="n"/>
+      <c r="M32" s="14" t="n"/>
+      <c r="N32" s="15" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="14" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="14" t="n"/>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="14" t="n"/>
+      <c r="L33" s="14" t="n"/>
+      <c r="M33" s="14" t="n"/>
+      <c r="N33" s="15" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="14" t="n"/>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="14" t="n"/>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="14" t="n"/>
+      <c r="N34" s="15" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="14" t="n"/>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="14" t="n"/>
+      <c r="J35" s="14" t="n"/>
+      <c r="K35" s="14" t="n"/>
+      <c r="L35" s="14" t="n"/>
+      <c r="M35" s="14" t="n"/>
+      <c r="N35" s="15" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="14" t="n"/>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="14" t="n"/>
+      <c r="L36" s="14" t="n"/>
+      <c r="M36" s="14" t="n"/>
+      <c r="N36" s="15" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="14" t="n"/>
+      <c r="L37" s="14" t="n"/>
+      <c r="M37" s="14" t="n"/>
+      <c r="N37" s="15" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="14" t="n"/>
+      <c r="J38" s="14" t="n"/>
+      <c r="K38" s="14" t="n"/>
+      <c r="L38" s="14" t="n"/>
+      <c r="M38" s="14" t="n"/>
+      <c r="N38" s="15" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="14" t="n"/>
+      <c r="H39" s="14" t="n"/>
+      <c r="I39" s="14" t="n"/>
+      <c r="J39" s="14" t="n"/>
+      <c r="K39" s="14" t="n"/>
+      <c r="L39" s="14" t="n"/>
+      <c r="M39" s="14" t="n"/>
+      <c r="N39" s="15" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="14" t="n"/>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="14" t="n"/>
+      <c r="G40" s="14" t="n"/>
+      <c r="H40" s="14" t="n"/>
+      <c r="I40" s="14" t="n"/>
+      <c r="J40" s="14" t="n"/>
+      <c r="K40" s="14" t="n"/>
+      <c r="L40" s="14" t="n"/>
+      <c r="M40" s="14" t="n"/>
+      <c r="N40" s="15" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="14" t="n"/>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="14" t="n"/>
+      <c r="G41" s="14" t="n"/>
+      <c r="H41" s="14" t="n"/>
+      <c r="I41" s="14" t="n"/>
+      <c r="J41" s="14" t="n"/>
+      <c r="K41" s="14" t="n"/>
+      <c r="L41" s="14" t="n"/>
+      <c r="M41" s="14" t="n"/>
+      <c r="N41" s="15" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="14" t="n"/>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="14" t="n"/>
+      <c r="J42" s="14" t="n"/>
+      <c r="K42" s="14" t="n"/>
+      <c r="L42" s="14" t="n"/>
+      <c r="M42" s="14" t="n"/>
+      <c r="N42" s="15" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="14" t="n"/>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="14" t="n"/>
+      <c r="F43" s="14" t="n"/>
+      <c r="G43" s="14" t="n"/>
+      <c r="H43" s="14" t="n"/>
+      <c r="I43" s="14" t="n"/>
+      <c r="J43" s="14" t="n"/>
+      <c r="K43" s="14" t="n"/>
+      <c r="L43" s="14" t="n"/>
+      <c r="M43" s="14" t="n"/>
+      <c r="N43" s="15" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="14" t="n"/>
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
+      <c r="G44" s="14" t="n"/>
+      <c r="H44" s="14" t="n"/>
+      <c r="I44" s="14" t="n"/>
+      <c r="J44" s="14" t="n"/>
+      <c r="K44" s="14" t="n"/>
+      <c r="L44" s="14" t="n"/>
+      <c r="M44" s="14" t="n"/>
+      <c r="N44" s="15" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46" ht="24.5" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>Este checklist es la VERIFICACIÓN DOCUMENTAL de la entrega (albarán, lote, etiquetado, envase, cantidad y quién la recibió). El PCC de temperatura vive en el registro 02: no se fusionan porque acreditan cosas distintas y se archivan por separado. Anota el mismo nº de lote en los dos para que la trazabilidad (registro 06) los enganche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="12.2" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>Archivar junto con los albaranes de entrega. Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="12.2" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A47:N47"/>
+    <mergeCell ref="A48:N48"/>
+    <mergeCell ref="A46:N46"/>
   </mergeCells>
+  <conditionalFormatting sqref="F5:I44">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>OR(F5="ALERTA",F5="RECHAZAR",F5="CAMBIAR",F5="REVISAR",F5="✗",F5="CADUCADO",F5="EXCESO")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+      <formula>OR(F5="VIGILAR",F5="⚠",F5="INCOMPLETO",F5="CADUCA PRONTO",F5="RENOVAR",F5="FALTA CLORO",F5="FALTA TEST")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>OR(F5="OK",F5="✓",F5="Cumple",F5="VIGENTE",F5="Completo",F5="APTO")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J44">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
+      <formula>OR(J5="ALERTA",J5="RECHAZAR",J5="CAMBIAR",J5="REVISAR",J5="✗",J5="CADUCADO",J5="EXCESO",J5="NO")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
+      <formula>OR(J5="VIGILAR",J5="⚠",J5="INCOMPLETO",J5="CADUCA PRONTO",J5="RENOVAR",J5="FALTA CLORO",J5="FALTA TEST")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
+      <formula>OR(J5="OK",J5="✓",J5="Cumple",J5="VIGENTE",J5="Completo",J5="APTO",J5="SÍ")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,✗"</formula1>
+    <dataValidation sqref="F5:F44 G5:G44 H5:H44 I5:I44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Verificación" error="Marca ✓ (conforme), ✗ (no conforme) o N/A. Si escribes otra cosa, el semáforo no la reconoce." type="list" errorStyle="stop">
+      <formula1>"✓,✗,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Aceptado" error="Escribe SÍ o NO." type="list" errorStyle="stop">
       <formula1>"SÍ,NO"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>

--- a/astro-site/public/dl/pack-appcc/05-checklist-recepcion-mercancias.xlsx
+++ b/astro-site/public/dl/pack-appcc/05-checklist-recepcion-mercancias.xlsx
@@ -1723,8 +1723,8 @@
   <mergeCells count="4">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A47:N47"/>
+    <mergeCell ref="A46:N46"/>
     <mergeCell ref="A48:N48"/>
-    <mergeCell ref="A46:N46"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:I44">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
